--- a/student_scores.xlsx
+++ b/student_scores.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scores" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,22 +429,52 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Remarks</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Ceejay</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>88</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>87</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>73</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
